--- a/Old Documents/Categorization of CIHR Funding Programs.xlsx
+++ b/Old Documents/Categorization of CIHR Funding Programs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcmasteru365.sharepoint.com/sites/targetedinnovationfunding/Shared Documents/4/Funding Recipients-Related Research/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcmasteru365-my.sharepoint.com/personal/choit7_mcmaster_ca/Documents/MacBook Desktop/CIHR Research/CIHR GitHub/Old Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{79B2BD66-68E4-4200-8438-02CF51F92E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27FCF256-6FB8-4C21-A969-CF1E1BC712AA}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{79B2BD66-68E4-4200-8438-02CF51F92E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0874325C-93B3-E94B-AA20-B062EF196B0E}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{A70B40B0-617D-45D8-A848-38FA8EEA24AA}"/>
+    <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="17020" xr2:uid="{A70B40B0-617D-45D8-A848-38FA8EEA24AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="120">
   <si>
     <t>Commercialization</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Clinical Trials (Operating and Project Grant Categories)</t>
   </si>
   <si>
-    <t xml:space="preserve">Advancing Technology Innovation Through Discovery </t>
-  </si>
-  <si>
     <t>Collaborative Health Research Projects - NSERC Partnered</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>Proof of Principle</t>
   </si>
   <si>
-    <t>Advancing Technology Innovation Through Discovery - Institute of Cancer Research</t>
-  </si>
-  <si>
     <t>Industry Partnered Collaborative Research</t>
   </si>
   <si>
@@ -116,21 +110,12 @@
     <t xml:space="preserve">Biochemistry &amp; Molecular Biology - A </t>
   </si>
   <si>
-    <t>Cancer progression and therapeutics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Biochemistry &amp; Molecular Biology - B </t>
   </si>
   <si>
-    <t>Cancer progression and therapeutics 2</t>
-  </si>
-  <si>
     <t>Biological and Clinical Aspects of Aging</t>
   </si>
   <si>
-    <t>Catalyst Grant : Biomedical Research for HIV/AIDS and STBBI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Biological and Clinical Aspects of Aging 2 </t>
   </si>
   <si>
@@ -194,27 +179,15 @@
     <t xml:space="preserve">Cell Physiology </t>
   </si>
   <si>
-    <t>Operating Grant - E-Rare-2: Innovative Therapeutic Approaches </t>
-  </si>
-  <si>
     <t xml:space="preserve">Cell and Developmental Physiology </t>
   </si>
   <si>
-    <t>Operating Grant: COVID-19 - Diagnostics</t>
-  </si>
-  <si>
     <t>Clinical Investigation - A: Reproduction, Maternal, Child and Youth Health</t>
   </si>
   <si>
-    <t>Operating Grant: COVID-19 - Therapeutics</t>
-  </si>
-  <si>
     <t>Clinical Investigation - A: Reproduction, Maternal, Child and Youth Health 2</t>
   </si>
   <si>
-    <t>Operating Grant: COVID-19 - Vaccines</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clinical Investigation - B 2 </t>
   </si>
   <si>
@@ -236,19 +209,10 @@
     <t xml:space="preserve">Clinical Investigation - D 2 </t>
   </si>
   <si>
-    <t>Catalyst Grant: Development and validation of new biomedical techniques and technologies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clinical Investigation - D: Cardiovascular Systems </t>
   </si>
   <si>
-    <t>Operating Grant - Priority Announcement Canadian HIV Vaccine Initiative</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dental Sciences </t>
-  </si>
-  <si>
-    <t>Targeting High Fatality Cancers Innovation Grant</t>
   </si>
   <si>
     <t xml:space="preserve">Developmental Biology </t>
@@ -426,12 +390,39 @@
       <t xml:space="preserve"> commercialization, collaboration, innovation, discovery, technologies, therapeutics, inventions</t>
     </r>
   </si>
+  <si>
+    <t>Canadian 2019 Novel Coronavirus (2019-nCoV) Rapid Research</t>
+  </si>
+  <si>
+    <t>Cancer Progression &amp; Therapeutics</t>
+  </si>
+  <si>
+    <t>Cancer Progression &amp; Therapeutics 2</t>
+  </si>
+  <si>
+    <t>Special Cases</t>
+  </si>
+  <si>
+    <t>Virology &amp; Viral Pathogenesis</t>
+  </si>
+  <si>
+    <t>Special Cases:</t>
+  </si>
+  <si>
+    <t>Advancing Technology Innovation Through Discovery</t>
+  </si>
+  <si>
+    <t>Advancing Technology Innovation through Discovery - Institute of Cancer Research</t>
+  </si>
+  <si>
+    <t>Operating Grant - E-Rare-2: Innovative Therapeutic Approaches</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,25 +439,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -538,12 +523,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -880,16 +863,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227CC4DD-963F-44A1-BE04-5CDCD8FB5D53}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E87"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="44.42578125" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="4" max="4" width="44.5" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.45" thickBot="1">
+    <row r="1" spans="1:5" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -906,806 +889,818 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29.1">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="29.1">
-      <c r="A3" s="6" t="s">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="6"/>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="6"/>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="29.1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="6"/>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" ht="29.1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
-      <c r="B8" s="6" t="s">
-        <v>26</v>
+      <c r="B8" t="s">
+        <v>113</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="6"/>
+      <c r="B9" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="6"/>
+      <c r="B10" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" ht="29.1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="6"/>
+      <c r="B11" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="6"/>
+      <c r="B12" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
-      <c r="B13" s="7" t="s">
-        <v>36</v>
+      <c r="B13" t="s">
+        <v>37</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
-      <c r="B14" s="7" t="s">
-        <v>38</v>
+      <c r="B14" t="s">
+        <v>35</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="6"/>
+      <c r="B15" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="6"/>
+      <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="D16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="6"/>
+      <c r="B17" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
-      <c r="B18" s="6" t="s">
-        <v>46</v>
+      <c r="B18" t="s">
+        <v>51</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
-      <c r="B19" s="6" t="s">
-        <v>48</v>
+      <c r="B19" t="s">
+        <v>53</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:5" ht="29.1">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
-      <c r="B20" s="6" t="s">
-        <v>50</v>
+      <c r="B20" t="s">
+        <v>114</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E20" s="6"/>
     </row>
-    <row r="21" spans="1:5" ht="29.1">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
-      <c r="B21" s="6" t="s">
-        <v>52</v>
+      <c r="B21" t="s">
+        <v>55</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" spans="1:5" ht="29.1">
+    <row r="22" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
-      <c r="B22" s="7" t="s">
-        <v>54</v>
+      <c r="B22" t="s">
+        <v>115</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" spans="1:5" ht="29.1">
+    <row r="23" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
-      <c r="B23" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
-      <c r="B24" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="B24" s="7"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="1:5" ht="29.1">
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
-      <c r="B25" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="B25" s="7"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" spans="1:5" ht="29.1">
+    <row r="26" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
-      <c r="B26" s="6" t="s">
-        <v>62</v>
+      <c r="B26" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
-      <c r="B27" s="6" t="s">
-        <v>64</v>
+      <c r="B27" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="1:5" ht="29.25">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="8" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" spans="1:5" ht="29.25">
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
-      <c r="B29" s="6" t="s">
-        <v>68</v>
+      <c r="B29" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
-      <c r="B30" t="s">
-        <v>70</v>
+      <c r="B30" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
+      <c r="B31" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
+      <c r="B32" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E32" s="6"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
+      <c r="B33" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E33" s="6"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
+      <c r="B34" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E34" s="6"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
+      <c r="B35" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E35" s="6"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
+      <c r="B36" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="C36" s="6"/>
       <c r="D36" s="6" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
+      <c r="B37" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E37" s="6"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
+      <c r="B38" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E38" s="6"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
+      <c r="B39" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E39" s="6"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E41" s="6"/>
     </row>
-    <row r="42" spans="1:5" ht="29.1">
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E42" s="6"/>
     </row>
-    <row r="43" spans="1:5" ht="29.1">
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E43" s="6"/>
     </row>
-    <row r="44" spans="1:5" ht="29.1">
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E44" s="6"/>
     </row>
-    <row r="45" spans="1:5" ht="29.1">
+    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E45" s="6"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E46" s="6"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E52" s="6"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E53" s="6"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E54" s="6"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E55" s="6"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E56" s="6"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E57" s="6"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E58" s="6"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E59" s="6"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E60" s="6"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E61" s="6"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E63" s="6"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E64" s="6"/>
     </row>
-    <row r="65" spans="1:5" ht="29.1">
+    <row r="65" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E65" s="6"/>
     </row>
-    <row r="66" spans="1:5" ht="29.1">
+    <row r="66" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E66" s="6"/>
     </row>
-    <row r="67" spans="1:5" ht="29.1">
+    <row r="67" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E67" s="6"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E68" s="6"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E69" s="6"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E70" s="6"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E71" s="6"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E72" s="6"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
       <c r="D73" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E73" s="6"/>
     </row>
-    <row r="74" spans="1:5" ht="29.1">
+    <row r="74" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
       <c r="D74" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E74" s="6"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E75" s="6"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
       <c r="D76" s="6" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E76" s="6"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
       <c r="D77" s="6" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E77" s="6"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
       <c r="D78" s="6" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E78" s="6"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
       <c r="D79" s="6" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E79" s="6"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
       <c r="D80" s="6" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E80" s="6"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
       <c r="E81" s="6"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
     </row>
-    <row r="87" spans="1:5" ht="87">
+    <row r="87" spans="1:5" ht="80" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1718,12 +1713,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005F7FD2BC003D584BB21DD38425BC03A1" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a13558884cf16fe63c45b09ba0b177fe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f9abba5c-c6ac-40f6-9bce-df6fe0d5849d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="024070713647e44e29b9722142610afe" ns2:_="">
     <xsd:import namespace="f9abba5c-c6ac-40f6-9bce-df6fe0d5849d"/>
@@ -1861,6 +1850,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1871,13 +1866,43 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF42F4C-2613-4004-81C7-1D7D9F2CC0CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17330931-B93C-4F5F-868E-9B5A49C3FA52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f9abba5c-c6ac-40f6-9bce-df6fe0d5849d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17330931-B93C-4F5F-868E-9B5A49C3FA52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF42F4C-2613-4004-81C7-1D7D9F2CC0CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f9abba5c-c6ac-40f6-9bce-df6fe0d5849d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B365BA83-DD60-4B2B-ADCC-9043DFF568B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B365BA83-DD60-4B2B-ADCC-9043DFF568B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>